--- a/Hardware/Running_Hardware/Open_STMPLC_Main_V0.1/bom/Main_PCB_BOM.xlsx
+++ b/Hardware/Running_Hardware/Open_STMPLC_Main_V0.1/bom/Main_PCB_BOM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/319af35e91399a73/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Open_PLCSTM32\Open_STMPLC\Hardware\Running_Hardware\Open_STMPLC_Main_V0.1\bom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47" documentId="8_{BD975CAA-BD92-49BF-B5C2-27A09DC911BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F0D7E59-DD55-4C45-BF97-A5E0E75B7CAA}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAEF87BE-C1F3-4AD4-932D-D3FA4B04B8B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{668EF1A7-AE68-40ED-912B-33E15B7C5C25}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="203">
   <si>
     <t>null</t>
   </si>
@@ -65,9 +65,6 @@
     <t>Quantity</t>
   </si>
   <si>
-    <t>C1, C5, C6, C8, C9, C10, C11, C12, C13, C14, C16, C17, C18, C21, C22, C23, C24, C26, C30, C31, C33, C34, C38, C39, C40, C41, C44, C45, C51, C53, C54, C59, C60, C63, C80</t>
-  </si>
-  <si>
     <t>100nF</t>
   </si>
   <si>
@@ -80,9 +77,6 @@
     <t>10pF</t>
   </si>
   <si>
-    <t>C4, C25, C27, C32, C35, C79</t>
-  </si>
-  <si>
     <t>10uF</t>
   </si>
   <si>
@@ -125,9 +119,6 @@
     <t>CP_EIA-3528-15_AVX-H</t>
   </si>
   <si>
-    <t>C55, C56</t>
-  </si>
-  <si>
     <t>22uF</t>
   </si>
   <si>
@@ -212,9 +203,6 @@
     <t>L_Abracon_ASPI-0630LR</t>
   </si>
   <si>
-    <t>D2, D3, D4, D7, D8, D92</t>
-  </si>
-  <si>
     <t>SMF5V0A</t>
   </si>
   <si>
@@ -278,9 +266,6 @@
     <t>U5</t>
   </si>
   <si>
-    <t>AP63203WU</t>
-  </si>
-  <si>
     <t>TSOT-23-6</t>
   </si>
   <si>
@@ -380,9 +365,6 @@
     <t>BatteryHolder_MYOUNG_BS-07-A1BJ001_CR2032</t>
   </si>
   <si>
-    <t>J8, J9, J10</t>
-  </si>
-  <si>
     <t>10144518-041802LF</t>
   </si>
   <si>
@@ -440,9 +422,6 @@
     <t>HY951180A</t>
   </si>
   <si>
-    <t>Vendor</t>
-  </si>
-  <si>
     <t>C1972946</t>
   </si>
   <si>
@@ -458,9 +437,6 @@
     <t>C84681</t>
   </si>
   <si>
-    <t>C780769</t>
-  </si>
-  <si>
     <t>C179171</t>
   </si>
   <si>
@@ -570,6 +546,108 @@
   </si>
   <si>
     <t>C91145</t>
+  </si>
+  <si>
+    <t>JLC Part number</t>
+  </si>
+  <si>
+    <t>C1, C5, C6, C8, C9, C10, C11, C12, C13, C14, C16, C17, C18, C21, C22, C23, C24, C26, C30, C31, C33, C34, C38, C39, C40, C41, C44, C45, C51, C53, C54, C59, C60, C63, C65, C70, C80</t>
+  </si>
+  <si>
+    <t>C4, C25, C27, C32, C35, C66, C71, C72, C79</t>
+  </si>
+  <si>
+    <t>C55, C56, C67, C68</t>
+  </si>
+  <si>
+    <t>C69</t>
+  </si>
+  <si>
+    <t>100pF</t>
+  </si>
+  <si>
+    <t>C73</t>
+  </si>
+  <si>
+    <t>1nF/2kV</t>
+  </si>
+  <si>
+    <t>C_1206_3216Metric_Pad1.33x1.80mm_HandSolder</t>
+  </si>
+  <si>
+    <t>R30</t>
+  </si>
+  <si>
+    <t>1M</t>
+  </si>
+  <si>
+    <t>R_1206_3216Metric_Pad1.30x1.75mm_HandSolder</t>
+  </si>
+  <si>
+    <t>D92</t>
+  </si>
+  <si>
+    <t>D2, D3, D4, D5, D6, D7, D8, D9, D10, D11, D12, D13, D14, D15, D16, D17, D18, D19, D20, D21, D22, D23, D24, D25, D26, D27, D28, D29, D30, D31</t>
+  </si>
+  <si>
+    <t>UAD8C05L01</t>
+  </si>
+  <si>
+    <t>D_SOD-882</t>
+  </si>
+  <si>
+    <t>U11, U12</t>
+  </si>
+  <si>
+    <t>SRV05-4</t>
+  </si>
+  <si>
+    <t>SOT-23-6</t>
+  </si>
+  <si>
+    <t>AMS1117-3.3</t>
+  </si>
+  <si>
+    <t>SOT-223-3_TabPin2</t>
+  </si>
+  <si>
+    <t>U9</t>
+  </si>
+  <si>
+    <t>AP63200WU</t>
+  </si>
+  <si>
+    <t>U10</t>
+  </si>
+  <si>
+    <t>AP63205WU</t>
+  </si>
+  <si>
+    <t>C14858</t>
+  </si>
+  <si>
+    <t>C23631</t>
+  </si>
+  <si>
+    <t>C2907441</t>
+  </si>
+  <si>
+    <t>C523533</t>
+  </si>
+  <si>
+    <t>C917183</t>
+  </si>
+  <si>
+    <t>C20615829</t>
+  </si>
+  <si>
+    <t>C2071868</t>
+  </si>
+  <si>
+    <t>C2071056</t>
+  </si>
+  <si>
+    <t>`</t>
   </si>
 </sst>
 </file>
@@ -941,12 +1019,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECB690C2-3395-4278-B9D4-884A5CEB0D73}">
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="4" max="4" width="146.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="34" customWidth="1"/>
     <col min="6" max="6" width="28.140625" customWidth="1"/>
     <col min="7" max="7" width="15.28515625" customWidth="1"/>
+    <col min="9" max="9" width="15.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -975,7 +1055,7 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>133</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -983,19 +1063,19 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
       <c r="H2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I2" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -1003,19 +1083,19 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H3">
         <v>7</v>
       </c>
       <c r="I3" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -1023,19 +1103,19 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
+        <v>171</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
         <v>13</v>
       </c>
-      <c r="E4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" t="s">
-        <v>15</v>
-      </c>
       <c r="H4">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I4" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -1043,19 +1123,19 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H5">
         <v>4</v>
       </c>
       <c r="I5" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -1063,19 +1143,19 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H6">
         <v>3</v>
       </c>
       <c r="I6" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -1083,19 +1163,19 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H7">
         <v>2</v>
       </c>
       <c r="I7" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -1103,22 +1183,22 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" t="s">
         <v>22</v>
-      </c>
-      <c r="E8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" t="s">
-        <v>24</v>
       </c>
       <c r="H8">
         <v>2</v>
       </c>
       <c r="I8" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -1126,19 +1206,19 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" t="s">
         <v>25</v>
-      </c>
-      <c r="E9" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" t="s">
-        <v>27</v>
       </c>
       <c r="H9">
         <v>2</v>
       </c>
       <c r="I9" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -1146,19 +1226,19 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>28</v>
+        <v>172</v>
       </c>
       <c r="E10" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F10" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I10" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -1166,573 +1246,576 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H11">
         <v>2</v>
       </c>
       <c r="I11" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>32</v>
+        <v>173</v>
       </c>
       <c r="E12" t="s">
-        <v>33</v>
+        <v>174</v>
       </c>
       <c r="F12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H12">
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>149</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>34</v>
+        <v>175</v>
       </c>
       <c r="E13" t="s">
-        <v>35</v>
+        <v>176</v>
       </c>
       <c r="F13" t="s">
-        <v>36</v>
+        <v>177</v>
       </c>
       <c r="H13">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>150</v>
+        <v>195</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E14" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F14" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="H14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E15" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F15" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H15">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="I15" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="E16" t="s">
         <v>35</v>
       </c>
       <c r="F16" t="s">
-        <v>36</v>
-      </c>
-      <c r="G16" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="H16">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I16" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E17" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F17" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I17" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D18" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E18" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="F18" t="s">
-        <v>36</v>
+        <v>33</v>
+      </c>
+      <c r="G18" t="s">
+        <v>22</v>
       </c>
       <c r="H18">
         <v>2</v>
       </c>
       <c r="I18" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D19" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="E19" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F19" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H19">
         <v>2</v>
       </c>
       <c r="I19" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D20" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E20" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F20" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I20" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D21" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E21" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F21" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I21" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D22" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="E22" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="F22" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H22">
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D23" t="s">
-        <v>54</v>
+        <v>178</v>
       </c>
       <c r="E23" t="s">
-        <v>55</v>
+        <v>179</v>
       </c>
       <c r="F23" t="s">
-        <v>56</v>
+        <v>180</v>
       </c>
       <c r="H23">
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>164</v>
+        <v>196</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D24" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="E24" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="F24" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="H24">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D25" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E25" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="F25" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="H25">
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D26" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="E26" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="F26" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="H26">
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D27" t="s">
-        <v>66</v>
+        <v>181</v>
       </c>
       <c r="E27" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="F27" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="H27">
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>166</v>
+        <v>127</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D28" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="E28" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="F28" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="H28">
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D29" t="s">
-        <v>72</v>
+        <v>182</v>
       </c>
       <c r="E29" t="s">
-        <v>73</v>
+        <v>183</v>
       </c>
       <c r="F29" t="s">
-        <v>74</v>
+        <v>184</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="I29" t="s">
-        <v>137</v>
+        <v>197</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D30" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="E30" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="F30" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="H30">
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D31" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="E31" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="F31" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="H31">
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D32" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="E32" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="F32" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="H32">
         <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D33" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="E33" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="F33" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="H33">
         <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D34" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E34" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="F34" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="H34">
         <v>1</v>
+      </c>
+      <c r="I34" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D35" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="E35" t="s">
-        <v>91</v>
+        <v>188</v>
       </c>
       <c r="F35" t="s">
-        <v>92</v>
+        <v>189</v>
       </c>
       <c r="H35">
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D36" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="E36" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="F36" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="H36">
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D37" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="E37" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="F37" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H37">
         <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>168</v>
+        <v>133</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D38" t="s">
-        <v>98</v>
+        <v>185</v>
       </c>
       <c r="E38" t="s">
-        <v>99</v>
+        <v>186</v>
       </c>
       <c r="F38" t="s">
-        <v>100</v>
+        <v>187</v>
       </c>
       <c r="H38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I38" t="s">
-        <v>170</v>
+        <v>199</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D39" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="E39" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="F39" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="H39">
         <v>1</v>
@@ -1740,196 +1823,333 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D40" t="s">
-        <v>104</v>
+        <v>190</v>
       </c>
       <c r="E40" t="s">
-        <v>105</v>
+        <v>191</v>
       </c>
       <c r="F40" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="H40">
         <v>1</v>
+      </c>
+      <c r="I40" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D41" t="s">
-        <v>107</v>
+        <v>192</v>
       </c>
       <c r="E41" t="s">
-        <v>108</v>
+        <v>193</v>
       </c>
       <c r="F41" t="s">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="H41">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>142</v>
+        <v>201</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D42" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="E42" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="F42" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="H42">
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D43" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="E43" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="F43" t="s">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="H43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D44" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="E44" t="s">
-        <v>117</v>
+        <v>92</v>
       </c>
       <c r="F44" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="H44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D45" t="s">
-        <v>119</v>
+        <v>93</v>
       </c>
       <c r="E45" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="F45" t="s">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="H45">
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D46" t="s">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="E46" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="F46" t="s">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="H46">
         <v>1</v>
-      </c>
-      <c r="I46" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="D47" t="s">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="E47" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="F47" t="s">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="H47">
         <v>1</v>
-      </c>
-      <c r="I47" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D48" t="s">
-        <v>128</v>
+        <v>102</v>
       </c>
       <c r="E48" t="s">
-        <v>129</v>
+        <v>103</v>
       </c>
       <c r="F48" t="s">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="H48">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="I48" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49">
+        <v>41</v>
+      </c>
+      <c r="D49" t="s">
+        <v>105</v>
+      </c>
+      <c r="E49" t="s">
+        <v>106</v>
+      </c>
+      <c r="F49" t="s">
+        <v>107</v>
+      </c>
+      <c r="H49">
+        <v>1</v>
+      </c>
+      <c r="I49" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>42</v>
+      </c>
+      <c r="D50" t="s">
+        <v>202</v>
+      </c>
+      <c r="E50" t="s">
+        <v>108</v>
+      </c>
+      <c r="F50" t="s">
+        <v>109</v>
+      </c>
+      <c r="H50">
+        <v>3</v>
+      </c>
+      <c r="I50" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>43</v>
+      </c>
+      <c r="D51" t="s">
+        <v>110</v>
+      </c>
+      <c r="E51" t="s">
+        <v>111</v>
+      </c>
+      <c r="F51" t="s">
+        <v>112</v>
+      </c>
+      <c r="H51">
+        <v>2</v>
+      </c>
+      <c r="I51" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>44</v>
+      </c>
+      <c r="D52" t="s">
+        <v>113</v>
+      </c>
+      <c r="E52" t="s">
+        <v>114</v>
+      </c>
+      <c r="F52" t="s">
+        <v>115</v>
+      </c>
+      <c r="H52">
+        <v>1</v>
+      </c>
+      <c r="I52" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>45</v>
+      </c>
+      <c r="D53" t="s">
+        <v>116</v>
+      </c>
+      <c r="E53" t="s">
+        <v>117</v>
+      </c>
+      <c r="F53" t="s">
+        <v>118</v>
+      </c>
+      <c r="H53">
+        <v>1</v>
+      </c>
+      <c r="I53" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>46</v>
+      </c>
+      <c r="D54" t="s">
+        <v>119</v>
+      </c>
+      <c r="E54" t="s">
+        <v>120</v>
+      </c>
+      <c r="F54" t="s">
+        <v>121</v>
+      </c>
+      <c r="H54">
+        <v>1</v>
+      </c>
+      <c r="I54" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>47</v>
+      </c>
+      <c r="D55" t="s">
+        <v>122</v>
+      </c>
+      <c r="E55" t="s">
+        <v>123</v>
+      </c>
+      <c r="F55" t="s">
+        <v>124</v>
+      </c>
+      <c r="H55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56">
         <v>48</v>
       </c>
-      <c r="D49" t="s">
-        <v>131</v>
-      </c>
-      <c r="E49" t="s">
-        <v>132</v>
-      </c>
-      <c r="F49" t="s">
-        <v>132</v>
-      </c>
-      <c r="H49">
-        <v>1</v>
-      </c>
-      <c r="I49" t="s">
-        <v>143</v>
+      <c r="D56" t="s">
+        <v>125</v>
+      </c>
+      <c r="E56" t="s">
+        <v>126</v>
+      </c>
+      <c r="F56" t="s">
+        <v>126</v>
+      </c>
+      <c r="H56">
+        <v>1</v>
+      </c>
+      <c r="I56" t="s">
+        <v>135</v>
       </c>
     </row>
   </sheetData>
